--- a/project_docs/FamilyPulse_Feature_Tracker.xlsx
+++ b/project_docs/FamilyPulse_Feature_Tracker.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="119">
   <si>
     <t xml:space="preserve">FamilyPulse — Feature Backlog</t>
   </si>
@@ -282,6 +282,24 @@
   </si>
   <si>
     <t xml:space="preserve">Unlocked the Analytics page's "by category" breakdown, which wasn't meaningful until this landed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Color theme picker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Six named color palettes (Blue Rose, Sunny Meadow, Coral Reef, Ocean Pop, Berry Patch, Aurora) selectable in Settings, each a real two-tone Material 3 scheme, persisted per user.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kid-friendly by design — selection uses a ring + checkmark, not color alone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English / Finnish / Swedish localization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full app translation (206 strings) via flutter_localizations + intl, with a Language picker in Settings (System/English/Suomi/Svenska); dates and times are locale-aware via DateFormat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Also localized auth/family error messages, not just static UI labels.</t>
   </si>
   <si>
     <t xml:space="preserve">Recurring events &amp; reminders</t>
@@ -808,7 +826,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -896,8 +914,8 @@
         <v>13</v>
       </c>
       <c r="J5" s="8" t="n">
-        <f aca="false">COUNTIF(D5:D26,"Done")</f>
-        <v>17</v>
+        <f aca="false">COUNTIF(D5:D28,"Done")</f>
+        <v>19</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -926,7 +944,7 @@
         <v>19</v>
       </c>
       <c r="J6" s="8" t="n">
-        <f aca="false">COUNTIF(D5:D26,"Done (existing)")</f>
+        <f aca="false">COUNTIF(D5:D28,"Done (existing)")</f>
         <v>4</v>
       </c>
     </row>
@@ -956,7 +974,7 @@
         <v>24</v>
       </c>
       <c r="J7" s="8" t="n">
-        <f aca="false">COUNTIF(D5:D26,"Roadmap")</f>
+        <f aca="false">COUNTIF(D5:D28,"Roadmap")</f>
         <v>1</v>
       </c>
     </row>
@@ -986,8 +1004,8 @@
         <v>28</v>
       </c>
       <c r="J8" s="8" t="n">
-        <f aca="false">COUNTA(D5:D26)</f>
-        <v>22</v>
+        <f aca="false">COUNTA(D5:D28)</f>
+        <v>24</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1375,27 +1393,73 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
         <v>87</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="D26" s="9" t="s">
-        <v>24</v>
+      <c r="D26" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F26" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="G26" s="6" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
         <v>90</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1430,7 +1494,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1439,7 +1503,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1448,16 +1512,16 @@
     </row>
     <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>8</v>
@@ -1468,64 +1532,64 @@
         <v>15</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="6" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="6" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="6" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C10" s="5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D10" s="5" t="n">
         <f aca="false">SUM(D5:D8)</f>

--- a/project_docs/FamilyPulse_Feature_Tracker.xlsx
+++ b/project_docs/FamilyPulse_Feature_Tracker.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="122">
   <si>
     <t xml:space="preserve">FamilyPulse — Feature Backlog</t>
   </si>
@@ -300,6 +300,15 @@
   </si>
   <si>
     <t xml:space="preserve">Also localized auth/family error messages, not just static UI labels.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profile photo, age &amp; gender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edit Profile now includes an avatar (camera or gallery, uploaded to Firebase Storage) plus optional age and gender fields, shown on the Profile screen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storage rules restrict writes to your own file (5MB cap, images only); project upgraded to Blaze with a $1 budget alert so cost stays at $0.</t>
   </si>
   <si>
     <t xml:space="preserve">Recurring events &amp; reminders</t>
@@ -826,7 +835,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -914,8 +923,8 @@
         <v>13</v>
       </c>
       <c r="J5" s="8" t="n">
-        <f aca="false">COUNTIF(D5:D28,"Done")</f>
-        <v>19</v>
+        <f aca="false">COUNTIF(D5:D29,"Done")</f>
+        <v>20</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -944,7 +953,7 @@
         <v>19</v>
       </c>
       <c r="J6" s="8" t="n">
-        <f aca="false">COUNTIF(D5:D28,"Done (existing)")</f>
+        <f aca="false">COUNTIF(D5:D29,"Done (existing)")</f>
         <v>4</v>
       </c>
     </row>
@@ -974,7 +983,7 @@
         <v>24</v>
       </c>
       <c r="J7" s="8" t="n">
-        <f aca="false">COUNTIF(D5:D28,"Roadmap")</f>
+        <f aca="false">COUNTIF(D5:D29,"Roadmap")</f>
         <v>1</v>
       </c>
     </row>
@@ -1004,8 +1013,8 @@
         <v>28</v>
       </c>
       <c r="J8" s="8" t="n">
-        <f aca="false">COUNTA(D5:D28)</f>
-        <v>24</v>
+        <f aca="false">COUNTA(D5:D29)</f>
+        <v>25</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1416,7 +1425,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
         <v>90</v>
       </c>
@@ -1439,27 +1448,50 @@
         <v>92</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
         <v>93</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D28" s="9" t="s">
-        <v>24</v>
+      <c r="D28" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="G28" s="6" t="s">
+    </row>
+    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
         <v>96</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1494,7 +1526,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1503,7 +1535,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1512,16 +1544,16 @@
     </row>
     <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>8</v>
@@ -1532,64 +1564,64 @@
         <v>15</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C10" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D10" s="5" t="n">
         <f aca="false">SUM(D5:D8)</f>

--- a/project_docs/FamilyPulse_Feature_Tracker.xlsx
+++ b/project_docs/FamilyPulse_Feature_Tracker.xlsx
@@ -347,7 +347,7 @@
     <t xml:space="preserve">Firestore wiring for calendar &amp; events (create/edit/delete), validation and error/success UX across auth + event editor, Welcome screen and auth gating, sign-out relocation + confirmation, theme system + Settings screen, Firestore security-rules fix for first-time family joins, Analytics page, Free Time finder screen, Family Groups, expanded roles + parent-rename (with matching security rules), real event categories, nav drawer + Profile screen, CI build-failure email alerts, several bug fixes (dialog crash, family-code race, pre-commit hook).</t>
   </si>
   <si>
-    <t xml:space="preserve">Hours are an example placeholder format — fill in real logged hours.</t>
+    <t xml:space="preserve">Self-reported by Rex (as of Aug 26, 2026): ~200 hours total across research, core app build, Firebase/Storage setup, and CI/CD pipeline work. An estimate, not independently timestamped.</t>
   </si>
   <si>
     <t xml:space="preserve">Jimmy Söderström</t>
@@ -1471,7 +1471,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
         <v>96</v>
       </c>
@@ -1569,7 +1569,9 @@
       <c r="C5" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D5" s="10"/>
+      <c r="D5" s="10" t="n">
+        <v>200</v>
+      </c>
       <c r="E5" s="6" t="s">
         <v>108</v>
       </c>
@@ -1625,7 +1627,7 @@
       </c>
       <c r="D10" s="5" t="n">
         <f aca="false">SUM(D5:D8)</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
